--- a/00-TrainRnns/tau-9/Theta/BestModels-1l.xlsx
+++ b/00-TrainRnns/tau-9/Theta/BestModels-1l.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,542 +507,272 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>40</v>
+        <v>708</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_arch2_r0.01_Ld0.3_Lp0.7_seed9468</t>
+          <t>model_arch24_r0.9_Ld0.3_Lp0.7_seed134</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[24]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6275805489931388</v>
+        <v>0.5940847499688993</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7891762165550193</v>
+        <v>-0.1006627778273104</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.950084640985597</v>
+        <v>-2.022045612390346</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.941175332552783</v>
+        <v>-8.626921335599523</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.721906740383698</v>
+        <v>-1.952272900833557</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.215966284031606</v>
+        <v>-1.443588330708292</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4116150865129218</v>
+        <v>0.2043957885795371</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09107624180721186</v>
+        <v>0.4264248213848461</v>
       </c>
       <c r="L2" t="n">
-        <v>-8.872323780014286</v>
+        <v>-5.613829498134757</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6275805489931388</v>
+        <v>0.5940847499688993</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7891762165550193</v>
+        <v>-0.1006627778273104</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.288856517524811</v>
+        <v>-2.718262438243156</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2879363337172184</v>
+        <v>-1.04712731874876</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>224</v>
+        <v>139</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch8_r0.01_Ld0.3_Lp0.7_seed9940</t>
+          <t>model_arch5_r0.9_Ld0.3_Lp0.7_seed9940</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[8]</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6243588387616954</v>
+        <v>0.1921281048408479</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7220511689793574</v>
+        <v>0.4637268908459906</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.850089018615649</v>
+        <v>-0.1722238359735058</v>
       </c>
       <c r="G3" t="n">
-        <v>-13.55562080172159</v>
+        <v>-9.322556148931998</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.207555923090181</v>
+        <v>-7.8837393269005</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.580849668423308</v>
+        <v>-0.4474380301392242</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.579930516502077</v>
+        <v>-0.9803159584697374</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6068861132161341</v>
+        <v>-1.058202952919454</v>
       </c>
       <c r="L3" t="n">
-        <v>-6.207431515351516</v>
+        <v>-0.5813428859129359</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6243588387616954</v>
+        <v>0.1921281048408479</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7220511689793574</v>
+        <v>0.4637268908459906</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.339227332926884</v>
+        <v>-2.920831305606765</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3528824818946025</v>
+        <v>-1.11562714869562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>72</v>
+        <v>2080</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch3_r0.01_Ld0.3_Lp0.7_seed2302</t>
+          <t>model_arch70_r0.01_Ld0.3_Lp0.7_seed9468</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[70]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6675420864415454</v>
+        <v>0.6622333225244178</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8215408856830333</v>
+        <v>0.3111844631416127</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.554525733872609</v>
+        <v>-4.92944831631904</v>
       </c>
       <c r="G4" t="n">
-        <v>-15.25027644855553</v>
+        <v>-9.420835972388996</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.062741173005366</v>
+        <v>-1.096555377874685</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.698831868486125</v>
+        <v>-1.441273391360235</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.022822977412442</v>
+        <v>0.06583177055392764</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6976153620655948</v>
+        <v>0.3821600751728729</v>
       </c>
       <c r="L4" t="n">
-        <v>-6.175472033601272</v>
+        <v>-8.747576306410531</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6675420864415454</v>
+        <v>0.6622333225244178</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8215408856830333</v>
+        <v>0.3111844631416127</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.581007838981107</v>
+        <v>-3.598242502660955</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3659942907512351</v>
+        <v>-1.266799893262842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>129</v>
+        <v>1215</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch5_r0.9_Ld0.5_Lp0.5_seed9940</t>
+          <t>model_arch41_r0.9_Ld0.3_Lp0.7_seed9468</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[5]</t>
+          <t>[41]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7657132996572951</v>
+        <v>0.6594719840459277</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8478821003167842</v>
+        <v>0.2059960073449083</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.199217020940242</v>
+        <v>-3.825245952014678</v>
       </c>
       <c r="G5" t="n">
-        <v>-14.05698473409564</v>
+        <v>-9.735182365039233</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.210047699622897</v>
+        <v>-0.7365079574139688</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.002326887865527</v>
+        <v>-1.343713233202359</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5243771365457</v>
+        <v>0.02747945546295383</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7284798727455497</v>
+        <v>0.4788953652786329</v>
       </c>
       <c r="L5" t="n">
-        <v>-11.11286819663055</v>
+        <v>-9.894399274822478</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7657132996572951</v>
+        <v>0.6594719840459277</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8478821003167842</v>
+        <v>0.2059960073449083</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.76819168613643</v>
+        <v>-3.575524851678732</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.370221138277789</v>
+        <v>-1.320768454118969</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2080</v>
+        <v>1511</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch70_r0.01_Ld0.3_Lp0.7_seed9468</t>
+          <t>model_arch51_r0.01_Ld0.3_Lp0.7_seed9583</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[70]</t>
+          <t>[51]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6622333225244178</v>
+        <v>0.6869720286090918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3111844631416127</v>
+        <v>0.2533471319771965</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.92944831631904</v>
+        <v>-4.079809860260186</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.420835972388996</v>
+        <v>-10.58905382158763</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.096555377874685</v>
+        <v>-1.273880630464327</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.441273391360235</v>
+        <v>-2.263950352125697</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06583177055392764</v>
+        <v>0.07689698057884553</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3821600751728729</v>
+        <v>0.4538550321373679</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.747576306410531</v>
+        <v>-8.524839461896706</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6622333225244178</v>
+        <v>0.6869720286090918</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3111844631416127</v>
+        <v>0.2533471319771965</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.598242502660955</v>
+        <v>-3.742968873374047</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3710648726542</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>model_arch6_r0.01_Ld0.5_Lp0.5_seed2302</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[6]</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7463351800710445</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8943631566747239</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-5.643273639555454</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-11.80890320145197</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.935393634366013</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-1.480665686185767</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-2.770108500627902</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8009660445301477</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-12.58846153895862</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.7463351800710445</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.8943631566747239</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-5.06083430808794</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.3724774692671291</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>model_arch3_r0.9_Ld0.3_Lp0.7_seed2302</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[3]</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5801339979180733</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.6368783244063008</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-2.101101238082886</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-11.7791688687236</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-4.578037156649911</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-2.642860561601272</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-2.136613870984114</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.5530867228429599</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-7.997966499617487</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.5801339979180733</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.6368783244063008</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-4.383237353259473</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.3761036867448246</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>model_arch4_r0.9_Ld0.5_Lp0.5_seed9940</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[4]</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6595161743436959</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8535270655769368</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1.596710006372068</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-12.63589947492192</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-4.708190340843788</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-4.306738614280873</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-3.604091712994922</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.6613472998116992</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-9.819812546904494</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.6595161743436959</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.8535270655769368</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-5.144299342358053</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.3858180006329059</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>708</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>model_arch24_r0.9_Ld0.3_Lp0.7_seed134</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[24]</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.5940847499688993</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.1006627778273104</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-2.022045612390346</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-8.626921335599523</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-1.952272900833557</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.443588330708292</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.2043957885795371</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.4264248213848461</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-5.613829498134757</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.5940847499688993</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.1006627778273104</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-2.718262438243156</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.3873874199029227</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>2089</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>model_arch70_r0.9_Ld0.3_Lp0.7_seed9940</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[70]</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.7052841571095303</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.5065452266909993</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-5.089501964208065</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-9.087771376820479</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.2699235423527371</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-1.510837684388009</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.05166750267894094</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.5768503411007913</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-12.38124093406767</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.7052841571095303</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.5065452266909993</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-3.958679665436747</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.3948835749800783</v>
+        <v>-1.340270382542683</v>
       </c>
     </row>
   </sheetData>
